--- a/artfynd/A 12199-2024 artfynd.xlsx
+++ b/artfynd/A 12199-2024 artfynd.xlsx
@@ -1503,10 +1503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117980660</v>
+        <v>117980661</v>
       </c>
       <c r="B10" t="n">
-        <v>90766</v>
+        <v>78216</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1515,25 +1515,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593391</v>
+        <v>593366</v>
       </c>
       <c r="R10" t="n">
-        <v>6980611</v>
+        <v>6980480</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1605,10 +1605,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117980661</v>
+        <v>117980693</v>
       </c>
       <c r="B11" t="n">
-        <v>78216</v>
+        <v>97753</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1617,25 +1617,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1645,10 +1645,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593366</v>
+        <v>593593</v>
       </c>
       <c r="R11" t="n">
-        <v>6980480</v>
+        <v>6980314</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1707,10 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117980693</v>
+        <v>117980660</v>
       </c>
       <c r="B12" t="n">
-        <v>97753</v>
+        <v>90766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1719,25 +1719,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>71</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593593</v>
+        <v>593391</v>
       </c>
       <c r="R12" t="n">
-        <v>6980314</v>
+        <v>6980611</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2217,10 +2217,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117980708</v>
+        <v>117980628</v>
       </c>
       <c r="B17" t="n">
-        <v>91772</v>
+        <v>96791</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593268</v>
+        <v>593542</v>
       </c>
       <c r="R17" t="n">
-        <v>6980571</v>
+        <v>6980421</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2319,10 +2319,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117980628</v>
+        <v>117980708</v>
       </c>
       <c r="B18" t="n">
-        <v>96791</v>
+        <v>91772</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593542</v>
+        <v>593268</v>
       </c>
       <c r="R18" t="n">
-        <v>6980421</v>
+        <v>6980571</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117980627</v>
+        <v>117980631</v>
       </c>
       <c r="B19" t="n">
-        <v>96791</v>
+        <v>79589</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593480</v>
+        <v>593499</v>
       </c>
       <c r="R19" t="n">
-        <v>6980602</v>
+        <v>6980565</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117980631</v>
+        <v>117980663</v>
       </c>
       <c r="B20" t="n">
-        <v>79589</v>
+        <v>78216</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2535,25 +2535,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593499</v>
+        <v>593459</v>
       </c>
       <c r="R20" t="n">
-        <v>6980565</v>
+        <v>6980593</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117980663</v>
+        <v>117980605</v>
       </c>
       <c r="B21" t="n">
-        <v>78216</v>
+        <v>57287</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2641,34 +2641,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593459</v>
+        <v>593120</v>
       </c>
       <c r="R21" t="n">
-        <v>6980593</v>
+        <v>6980627</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2695,12 +2703,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2727,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117980605</v>
+        <v>117980674</v>
       </c>
       <c r="B22" t="n">
-        <v>57287</v>
+        <v>97836</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2739,46 +2747,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593120</v>
+        <v>593180</v>
       </c>
       <c r="R22" t="n">
-        <v>6980627</v>
+        <v>6980623</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2837,7 +2841,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117980674</v>
+        <v>117980673</v>
       </c>
       <c r="B23" t="n">
         <v>97836</v>
@@ -2872,7 +2876,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2881,10 +2885,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593180</v>
+        <v>593420</v>
       </c>
       <c r="R23" t="n">
-        <v>6980623</v>
+        <v>6980677</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2943,10 +2947,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117980673</v>
+        <v>117980627</v>
       </c>
       <c r="B24" t="n">
-        <v>97836</v>
+        <v>96791</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,42 +2959,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593420</v>
+        <v>593480</v>
       </c>
       <c r="R24" t="n">
-        <v>6980677</v>
+        <v>6980602</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3017,12 +3017,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 12199-2024 artfynd.xlsx
+++ b/artfynd/A 12199-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117980606</v>
+        <v>117980674</v>
       </c>
       <c r="B2" t="n">
-        <v>57287</v>
+        <v>97836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593081</v>
+        <v>593180</v>
       </c>
       <c r="R2" t="n">
-        <v>6980689</v>
+        <v>6980623</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117980588</v>
+        <v>117980628</v>
       </c>
       <c r="B3" t="n">
-        <v>79098</v>
+        <v>96791</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593474</v>
+        <v>593542</v>
       </c>
       <c r="R3" t="n">
-        <v>6980500</v>
+        <v>6980421</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -887,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117980598</v>
+        <v>117980638</v>
       </c>
       <c r="B4" t="n">
-        <v>90499</v>
+        <v>79561</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593571</v>
+        <v>593372</v>
       </c>
       <c r="R4" t="n">
-        <v>6980412</v>
+        <v>6980466</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -989,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117980668</v>
+        <v>117980632</v>
       </c>
       <c r="B5" t="n">
-        <v>97836</v>
+        <v>79589</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,42 +997,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593436</v>
+        <v>593485</v>
       </c>
       <c r="R5" t="n">
-        <v>6980668</v>
+        <v>6980576</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1063,12 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117980635</v>
+        <v>117980668</v>
       </c>
       <c r="B6" t="n">
-        <v>78217</v>
+        <v>97836</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,38 +1099,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593399</v>
+        <v>593436</v>
       </c>
       <c r="R6" t="n">
-        <v>6980616</v>
+        <v>6980668</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1197,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117980638</v>
+        <v>117980660</v>
       </c>
       <c r="B7" t="n">
-        <v>79561</v>
+        <v>90766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1209,25 +1205,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>71</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1237,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593372</v>
+        <v>593391</v>
       </c>
       <c r="R7" t="n">
-        <v>6980466</v>
+        <v>6980611</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1267,12 +1263,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117980664</v>
+        <v>117980582</v>
       </c>
       <c r="B8" t="n">
-        <v>78216</v>
+        <v>97870</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1311,25 +1307,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1339,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593399</v>
+        <v>593423</v>
       </c>
       <c r="R8" t="n">
-        <v>6980616</v>
+        <v>6980691</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1401,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117980595</v>
+        <v>117980662</v>
       </c>
       <c r="B9" t="n">
-        <v>79069</v>
+        <v>78216</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1417,21 +1413,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1441,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593356</v>
+        <v>593440</v>
       </c>
       <c r="R9" t="n">
-        <v>6980596</v>
+        <v>6980474</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1471,12 +1467,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117980661</v>
+        <v>117980595</v>
       </c>
       <c r="B10" t="n">
-        <v>78216</v>
+        <v>79069</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1519,21 +1515,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593366</v>
+        <v>593356</v>
       </c>
       <c r="R10" t="n">
-        <v>6980480</v>
+        <v>6980596</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1573,12 +1569,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1605,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117980693</v>
+        <v>117980627</v>
       </c>
       <c r="B11" t="n">
-        <v>97753</v>
+        <v>96791</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1621,21 +1617,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1645,10 +1641,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593593</v>
+        <v>593480</v>
       </c>
       <c r="R11" t="n">
-        <v>6980314</v>
+        <v>6980602</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1707,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117980660</v>
+        <v>117980631</v>
       </c>
       <c r="B12" t="n">
-        <v>90766</v>
+        <v>79589</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1719,25 +1715,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>71</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593391</v>
+        <v>593499</v>
       </c>
       <c r="R12" t="n">
-        <v>6980611</v>
+        <v>6980565</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1777,12 +1773,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117980665</v>
+        <v>117980682</v>
       </c>
       <c r="B13" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1825,21 +1821,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1849,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593179</v>
+        <v>593504</v>
       </c>
       <c r="R13" t="n">
-        <v>6980623</v>
+        <v>6980541</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1879,12 +1875,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1911,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117980639</v>
+        <v>117980635</v>
       </c>
       <c r="B14" t="n">
-        <v>79561</v>
+        <v>78217</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1927,21 +1923,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1951,10 +1947,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593532</v>
+        <v>593399</v>
       </c>
       <c r="R14" t="n">
-        <v>6980562</v>
+        <v>6980616</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1981,12 +1977,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,10 +2009,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117980633</v>
+        <v>117980669</v>
       </c>
       <c r="B15" t="n">
-        <v>78217</v>
+        <v>97836</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2025,38 +2021,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593472</v>
+        <v>593595</v>
       </c>
       <c r="R15" t="n">
-        <v>6980504</v>
+        <v>6980349</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2115,10 +2115,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117980687</v>
+        <v>117980581</v>
       </c>
       <c r="B16" t="n">
-        <v>78480</v>
+        <v>90425</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593132</v>
+        <v>593474</v>
       </c>
       <c r="R16" t="n">
-        <v>6980622</v>
+        <v>6980576</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2217,10 +2217,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117980628</v>
+        <v>117980705</v>
       </c>
       <c r="B17" t="n">
-        <v>96791</v>
+        <v>91772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593542</v>
+        <v>593583</v>
       </c>
       <c r="R17" t="n">
-        <v>6980421</v>
+        <v>6980599</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117980708</v>
+        <v>117980692</v>
       </c>
       <c r="B18" t="n">
-        <v>91772</v>
+        <v>97753</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593268</v>
+        <v>593483</v>
       </c>
       <c r="R18" t="n">
-        <v>6980571</v>
+        <v>6980576</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117980631</v>
+        <v>117980683</v>
       </c>
       <c r="B19" t="n">
-        <v>79589</v>
+        <v>78480</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2433,25 +2433,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593499</v>
+        <v>593440</v>
       </c>
       <c r="R19" t="n">
-        <v>6980565</v>
+        <v>6980524</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117980605</v>
+        <v>117980661</v>
       </c>
       <c r="B21" t="n">
-        <v>57287</v>
+        <v>78216</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2641,42 +2641,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593120</v>
+        <v>593366</v>
       </c>
       <c r="R21" t="n">
-        <v>6980627</v>
+        <v>6980480</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2703,12 +2695,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2735,10 +2727,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117980674</v>
+        <v>117980606</v>
       </c>
       <c r="B22" t="n">
-        <v>97836</v>
+        <v>57287</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,42 +2739,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593180</v>
+        <v>593081</v>
       </c>
       <c r="R22" t="n">
-        <v>6980623</v>
+        <v>6980689</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2841,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117980673</v>
+        <v>117980708</v>
       </c>
       <c r="B23" t="n">
-        <v>97836</v>
+        <v>91772</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,42 +2849,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593420</v>
+        <v>593268</v>
       </c>
       <c r="R23" t="n">
-        <v>6980677</v>
+        <v>6980571</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2947,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117980627</v>
+        <v>117980602</v>
       </c>
       <c r="B24" t="n">
-        <v>96791</v>
+        <v>57287</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,38 +2951,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593480</v>
+        <v>593465</v>
       </c>
       <c r="R24" t="n">
-        <v>6980602</v>
+        <v>6980521</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3049,10 +3053,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117980682</v>
+        <v>117980675</v>
       </c>
       <c r="B25" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3061,38 +3065,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593504</v>
+        <v>593115</v>
       </c>
       <c r="R25" t="n">
-        <v>6980541</v>
+        <v>6980664</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3119,12 +3127,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3151,10 +3159,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117980686</v>
+        <v>117980639</v>
       </c>
       <c r="B26" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3167,21 +3175,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3191,10 +3199,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593446</v>
+        <v>593532</v>
       </c>
       <c r="R26" t="n">
-        <v>6980643</v>
+        <v>6980562</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3221,12 +3229,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3253,10 +3261,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117980692</v>
+        <v>117980605</v>
       </c>
       <c r="B27" t="n">
-        <v>97753</v>
+        <v>57287</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,38 +3273,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593483</v>
+        <v>593120</v>
       </c>
       <c r="R27" t="n">
-        <v>6980576</v>
+        <v>6980627</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3323,12 +3339,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3355,10 +3371,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117980602</v>
+        <v>117980687</v>
       </c>
       <c r="B28" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3371,46 +3387,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593465</v>
+        <v>593132</v>
       </c>
       <c r="R28" t="n">
-        <v>6980521</v>
+        <v>6980622</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3437,12 +3441,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3469,10 +3473,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117980669</v>
+        <v>117980636</v>
       </c>
       <c r="B29" t="n">
-        <v>97836</v>
+        <v>78217</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3481,42 +3485,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593595</v>
+        <v>593034</v>
       </c>
       <c r="R29" t="n">
-        <v>6980349</v>
+        <v>6980700</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3543,12 +3543,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3575,10 +3575,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117980581</v>
+        <v>117980693</v>
       </c>
       <c r="B30" t="n">
-        <v>90425</v>
+        <v>97753</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3587,25 +3587,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3242</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593474</v>
+        <v>593593</v>
       </c>
       <c r="R30" t="n">
-        <v>6980576</v>
+        <v>6980314</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117980675</v>
+        <v>117980598</v>
       </c>
       <c r="B31" t="n">
-        <v>97836</v>
+        <v>90499</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3689,42 +3689,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>593115</v>
+        <v>593571</v>
       </c>
       <c r="R31" t="n">
-        <v>6980664</v>
+        <v>6980412</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3751,12 +3747,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3783,10 +3779,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117980662</v>
+        <v>117980588</v>
       </c>
       <c r="B32" t="n">
-        <v>78216</v>
+        <v>79098</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3799,21 +3795,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3823,10 +3819,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>593440</v>
+        <v>593474</v>
       </c>
       <c r="R32" t="n">
-        <v>6980474</v>
+        <v>6980500</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3885,7 +3881,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117980683</v>
+        <v>117980686</v>
       </c>
       <c r="B33" t="n">
         <v>78480</v>
@@ -3925,10 +3921,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>593440</v>
+        <v>593446</v>
       </c>
       <c r="R33" t="n">
-        <v>6980524</v>
+        <v>6980643</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3955,12 +3951,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3987,10 +3983,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117980705</v>
+        <v>117980664</v>
       </c>
       <c r="B34" t="n">
-        <v>91772</v>
+        <v>78216</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3999,25 +3995,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4027,10 +4023,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>593583</v>
+        <v>593399</v>
       </c>
       <c r="R34" t="n">
-        <v>6980599</v>
+        <v>6980616</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4057,12 +4053,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4089,10 +4085,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117980582</v>
+        <v>117980633</v>
       </c>
       <c r="B35" t="n">
-        <v>97870</v>
+        <v>78217</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4101,25 +4097,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219874</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4129,10 +4125,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>593423</v>
+        <v>593472</v>
       </c>
       <c r="R35" t="n">
-        <v>6980691</v>
+        <v>6980504</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4159,12 +4155,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4191,10 +4187,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117980632</v>
+        <v>117980665</v>
       </c>
       <c r="B36" t="n">
-        <v>79589</v>
+        <v>78216</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4203,25 +4199,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4231,10 +4227,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593485</v>
+        <v>593179</v>
       </c>
       <c r="R36" t="n">
-        <v>6980576</v>
+        <v>6980623</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4261,12 +4257,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4293,10 +4289,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117980636</v>
+        <v>117980673</v>
       </c>
       <c r="B37" t="n">
-        <v>78217</v>
+        <v>97836</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4305,38 +4301,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>593034</v>
+        <v>593420</v>
       </c>
       <c r="R37" t="n">
-        <v>6980700</v>
+        <v>6980677</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4395,10 +4395,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117980671</v>
+        <v>117980592</v>
       </c>
       <c r="B38" t="n">
-        <v>97836</v>
+        <v>79098</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4407,42 +4407,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>593416</v>
+        <v>593025</v>
       </c>
       <c r="R38" t="n">
-        <v>6980734</v>
+        <v>6980743</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4501,10 +4497,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117980592</v>
+        <v>117980671</v>
       </c>
       <c r="B39" t="n">
-        <v>79098</v>
+        <v>97836</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4513,38 +4509,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>593025</v>
+        <v>593416</v>
       </c>
       <c r="R39" t="n">
-        <v>6980743</v>
+        <v>6980734</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4603,10 +4603,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117980672</v>
+        <v>117980596</v>
       </c>
       <c r="B40" t="n">
-        <v>97836</v>
+        <v>79069</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4615,42 +4615,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>593402</v>
+        <v>593032</v>
       </c>
       <c r="R40" t="n">
-        <v>6980730</v>
+        <v>6980736</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4709,10 +4705,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117980596</v>
+        <v>117980672</v>
       </c>
       <c r="B41" t="n">
-        <v>79069</v>
+        <v>97836</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4721,38 +4717,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>593032</v>
+        <v>593402</v>
       </c>
       <c r="R41" t="n">
-        <v>6980736</v>
+        <v>6980730</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>

--- a/artfynd/A 12199-2024 artfynd.xlsx
+++ b/artfynd/A 12199-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117980674</v>
+        <v>117980602</v>
       </c>
       <c r="B2" t="n">
-        <v>97836</v>
+        <v>57288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593180</v>
+        <v>593465</v>
       </c>
       <c r="R2" t="n">
-        <v>6980623</v>
+        <v>6980521</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -749,12 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117980628</v>
+        <v>117980631</v>
       </c>
       <c r="B3" t="n">
-        <v>96791</v>
+        <v>79591</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593542</v>
+        <v>593499</v>
       </c>
       <c r="R3" t="n">
-        <v>6980421</v>
+        <v>6980565</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -883,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117980638</v>
+        <v>117980639</v>
       </c>
       <c r="B4" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593372</v>
+        <v>593532</v>
       </c>
       <c r="R4" t="n">
-        <v>6980466</v>
+        <v>6980562</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -988,7 +996,7 @@
         <v>117980632</v>
       </c>
       <c r="B5" t="n">
-        <v>79589</v>
+        <v>79591</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117980668</v>
+        <v>117980633</v>
       </c>
       <c r="B6" t="n">
-        <v>97836</v>
+        <v>78219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,42 +1107,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593436</v>
+        <v>593472</v>
       </c>
       <c r="R6" t="n">
-        <v>6980668</v>
+        <v>6980504</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1161,12 +1165,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117980660</v>
+        <v>117980595</v>
       </c>
       <c r="B7" t="n">
-        <v>90766</v>
+        <v>79071</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,25 +1209,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593391</v>
+        <v>593356</v>
       </c>
       <c r="R7" t="n">
-        <v>6980611</v>
+        <v>6980596</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1295,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117980582</v>
+        <v>117980693</v>
       </c>
       <c r="B8" t="n">
-        <v>97870</v>
+        <v>97755</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1311,21 +1315,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1335,10 +1339,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593423</v>
+        <v>593593</v>
       </c>
       <c r="R8" t="n">
-        <v>6980691</v>
+        <v>6980314</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1365,12 +1369,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117980662</v>
+        <v>117980627</v>
       </c>
       <c r="B9" t="n">
-        <v>78216</v>
+        <v>96793</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,25 +1413,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1437,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593440</v>
+        <v>593480</v>
       </c>
       <c r="R9" t="n">
-        <v>6980474</v>
+        <v>6980602</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1499,10 +1503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117980595</v>
+        <v>117980668</v>
       </c>
       <c r="B10" t="n">
-        <v>79069</v>
+        <v>97838</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,38 +1515,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593356</v>
+        <v>593436</v>
       </c>
       <c r="R10" t="n">
-        <v>6980596</v>
+        <v>6980668</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1601,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117980627</v>
+        <v>117980673</v>
       </c>
       <c r="B11" t="n">
-        <v>96791</v>
+        <v>97838</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1613,38 +1621,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593480</v>
+        <v>593420</v>
       </c>
       <c r="R11" t="n">
-        <v>6980602</v>
+        <v>6980677</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1671,12 +1683,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117980631</v>
+        <v>117980705</v>
       </c>
       <c r="B12" t="n">
-        <v>79589</v>
+        <v>91774</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1719,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593499</v>
+        <v>593583</v>
       </c>
       <c r="R12" t="n">
-        <v>6980565</v>
+        <v>6980599</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1805,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117980682</v>
+        <v>117980598</v>
       </c>
       <c r="B13" t="n">
-        <v>78480</v>
+        <v>90501</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1821,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1845,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593504</v>
+        <v>593571</v>
       </c>
       <c r="R13" t="n">
-        <v>6980541</v>
+        <v>6980412</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1907,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117980635</v>
+        <v>117980628</v>
       </c>
       <c r="B14" t="n">
-        <v>78217</v>
+        <v>96793</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1919,25 +1931,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1947,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593399</v>
+        <v>593542</v>
       </c>
       <c r="R14" t="n">
-        <v>6980616</v>
+        <v>6980421</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1977,12 +1989,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117980669</v>
+        <v>117980692</v>
       </c>
       <c r="B15" t="n">
-        <v>97836</v>
+        <v>97755</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2021,42 +2033,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593595</v>
+        <v>593483</v>
       </c>
       <c r="R15" t="n">
-        <v>6980349</v>
+        <v>6980576</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2115,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117980581</v>
+        <v>117980606</v>
       </c>
       <c r="B16" t="n">
-        <v>90425</v>
+        <v>57288</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2131,34 +2139,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3242</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593474</v>
+        <v>593081</v>
       </c>
       <c r="R16" t="n">
-        <v>6980576</v>
+        <v>6980689</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2185,12 +2201,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2217,10 +2233,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117980705</v>
+        <v>117980664</v>
       </c>
       <c r="B17" t="n">
-        <v>91772</v>
+        <v>78218</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2229,25 +2245,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2257,10 +2273,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593583</v>
+        <v>593399</v>
       </c>
       <c r="R17" t="n">
-        <v>6980599</v>
+        <v>6980616</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2287,12 +2303,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2319,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117980692</v>
+        <v>117980581</v>
       </c>
       <c r="B18" t="n">
-        <v>97753</v>
+        <v>90427</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2331,25 +2347,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>3242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2359,7 +2375,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593483</v>
+        <v>593474</v>
       </c>
       <c r="R18" t="n">
         <v>6980576</v>
@@ -2421,10 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117980683</v>
+        <v>117980682</v>
       </c>
       <c r="B19" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,10 +2477,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593440</v>
+        <v>593504</v>
       </c>
       <c r="R19" t="n">
-        <v>6980524</v>
+        <v>6980541</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2523,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117980663</v>
+        <v>117980662</v>
       </c>
       <c r="B20" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2563,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593459</v>
+        <v>593440</v>
       </c>
       <c r="R20" t="n">
-        <v>6980593</v>
+        <v>6980474</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2625,10 +2641,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117980661</v>
+        <v>117980663</v>
       </c>
       <c r="B21" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2665,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593366</v>
+        <v>593459</v>
       </c>
       <c r="R21" t="n">
-        <v>6980480</v>
+        <v>6980593</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2727,10 +2743,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117980606</v>
+        <v>117980636</v>
       </c>
       <c r="B22" t="n">
-        <v>57287</v>
+        <v>78219</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2743,42 +2759,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593081</v>
+        <v>593034</v>
       </c>
       <c r="R22" t="n">
-        <v>6980689</v>
+        <v>6980700</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2837,10 +2845,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117980708</v>
+        <v>117980683</v>
       </c>
       <c r="B23" t="n">
-        <v>91772</v>
+        <v>78482</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,25 +2857,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2885,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593268</v>
+        <v>593440</v>
       </c>
       <c r="R23" t="n">
-        <v>6980571</v>
+        <v>6980524</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2907,12 +2915,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2939,10 +2947,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117980602</v>
+        <v>117980605</v>
       </c>
       <c r="B24" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2972,11 +2980,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
@@ -2991,10 +2995,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593465</v>
+        <v>593120</v>
       </c>
       <c r="R24" t="n">
-        <v>6980521</v>
+        <v>6980627</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3021,12 +3025,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3053,10 +3057,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117980675</v>
+        <v>117980582</v>
       </c>
       <c r="B25" t="n">
-        <v>97836</v>
+        <v>97872</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3065,42 +3069,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593115</v>
+        <v>593423</v>
       </c>
       <c r="R25" t="n">
-        <v>6980664</v>
+        <v>6980691</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3159,10 +3159,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117980639</v>
+        <v>117980665</v>
       </c>
       <c r="B26" t="n">
-        <v>79561</v>
+        <v>78218</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3175,21 +3175,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593532</v>
+        <v>593179</v>
       </c>
       <c r="R26" t="n">
-        <v>6980562</v>
+        <v>6980623</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3261,10 +3261,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117980605</v>
+        <v>117980686</v>
       </c>
       <c r="B27" t="n">
-        <v>57287</v>
+        <v>78482</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3277,42 +3277,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593120</v>
+        <v>593446</v>
       </c>
       <c r="R27" t="n">
-        <v>6980627</v>
+        <v>6980643</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3371,10 +3363,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117980687</v>
+        <v>117980708</v>
       </c>
       <c r="B28" t="n">
-        <v>78480</v>
+        <v>91774</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3383,25 +3375,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3411,10 +3403,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593132</v>
+        <v>593268</v>
       </c>
       <c r="R28" t="n">
-        <v>6980622</v>
+        <v>6980571</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3473,10 +3465,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117980636</v>
+        <v>117980674</v>
       </c>
       <c r="B29" t="n">
-        <v>78217</v>
+        <v>97838</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3485,38 +3477,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593034</v>
+        <v>593180</v>
       </c>
       <c r="R29" t="n">
-        <v>6980700</v>
+        <v>6980623</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3575,10 +3571,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117980693</v>
+        <v>117980588</v>
       </c>
       <c r="B30" t="n">
-        <v>97753</v>
+        <v>79100</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3587,25 +3583,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3615,10 +3611,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593593</v>
+        <v>593474</v>
       </c>
       <c r="R30" t="n">
-        <v>6980314</v>
+        <v>6980500</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3677,10 +3673,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117980598</v>
+        <v>117980638</v>
       </c>
       <c r="B31" t="n">
-        <v>90499</v>
+        <v>79563</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3693,21 +3689,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3717,10 +3713,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>593571</v>
+        <v>593372</v>
       </c>
       <c r="R31" t="n">
-        <v>6980412</v>
+        <v>6980466</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3779,10 +3775,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117980588</v>
+        <v>117980669</v>
       </c>
       <c r="B32" t="n">
-        <v>79098</v>
+        <v>97838</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3791,38 +3787,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>593474</v>
+        <v>593595</v>
       </c>
       <c r="R32" t="n">
-        <v>6980500</v>
+        <v>6980349</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117980686</v>
+        <v>117980635</v>
       </c>
       <c r="B33" t="n">
-        <v>78480</v>
+        <v>78219</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3897,21 +3897,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>593446</v>
+        <v>593399</v>
       </c>
       <c r="R33" t="n">
-        <v>6980643</v>
+        <v>6980616</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3983,10 +3983,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117980664</v>
+        <v>117980660</v>
       </c>
       <c r="B34" t="n">
-        <v>78216</v>
+        <v>90768</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3995,25 +3995,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>71</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>593399</v>
+        <v>593391</v>
       </c>
       <c r="R34" t="n">
-        <v>6980616</v>
+        <v>6980611</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117980633</v>
+        <v>117980661</v>
       </c>
       <c r="B35" t="n">
-        <v>78217</v>
+        <v>78218</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4101,21 +4101,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>593472</v>
+        <v>593366</v>
       </c>
       <c r="R35" t="n">
-        <v>6980504</v>
+        <v>6980480</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4187,10 +4187,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117980665</v>
+        <v>117980687</v>
       </c>
       <c r="B36" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4203,21 +4203,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593179</v>
+        <v>593132</v>
       </c>
       <c r="R36" t="n">
-        <v>6980623</v>
+        <v>6980622</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4289,10 +4289,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117980673</v>
+        <v>117980675</v>
       </c>
       <c r="B37" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>593420</v>
+        <v>593115</v>
       </c>
       <c r="R37" t="n">
-        <v>6980677</v>
+        <v>6980664</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4398,7 +4398,7 @@
         <v>117980592</v>
       </c>
       <c r="B38" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4497,10 +4497,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117980671</v>
+        <v>117980596</v>
       </c>
       <c r="B39" t="n">
-        <v>97836</v>
+        <v>79071</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4509,42 +4509,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>593416</v>
+        <v>593032</v>
       </c>
       <c r="R39" t="n">
-        <v>6980734</v>
+        <v>6980736</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4603,10 +4599,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117980596</v>
+        <v>117980672</v>
       </c>
       <c r="B40" t="n">
-        <v>79069</v>
+        <v>97838</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4615,38 +4611,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>593032</v>
+        <v>593402</v>
       </c>
       <c r="R40" t="n">
-        <v>6980736</v>
+        <v>6980730</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4705,10 +4705,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117980672</v>
+        <v>117980671</v>
       </c>
       <c r="B41" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>593402</v>
+        <v>593416</v>
       </c>
       <c r="R41" t="n">
-        <v>6980730</v>
+        <v>6980734</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>

--- a/artfynd/A 12199-2024 artfynd.xlsx
+++ b/artfynd/A 12199-2024 artfynd.xlsx
@@ -2947,10 +2947,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117980605</v>
+        <v>117980582</v>
       </c>
       <c r="B24" t="n">
-        <v>57288</v>
+        <v>97872</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,46 +2959,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593120</v>
+        <v>593423</v>
       </c>
       <c r="R24" t="n">
-        <v>6980627</v>
+        <v>6980691</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3057,10 +3049,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117980582</v>
+        <v>117980605</v>
       </c>
       <c r="B25" t="n">
-        <v>97872</v>
+        <v>57288</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3069,38 +3061,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593423</v>
+        <v>593120</v>
       </c>
       <c r="R25" t="n">
-        <v>6980691</v>
+        <v>6980627</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3983,10 +3983,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117980660</v>
+        <v>117980661</v>
       </c>
       <c r="B34" t="n">
-        <v>90768</v>
+        <v>78218</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3995,25 +3995,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>71</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>593391</v>
+        <v>593366</v>
       </c>
       <c r="R34" t="n">
-        <v>6980611</v>
+        <v>6980480</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4085,10 +4085,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117980661</v>
+        <v>117980687</v>
       </c>
       <c r="B35" t="n">
-        <v>78218</v>
+        <v>78482</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4101,21 +4101,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>593366</v>
+        <v>593132</v>
       </c>
       <c r="R35" t="n">
-        <v>6980480</v>
+        <v>6980622</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4187,10 +4187,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117980687</v>
+        <v>117980660</v>
       </c>
       <c r="B36" t="n">
-        <v>78482</v>
+        <v>90768</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4199,25 +4199,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>71</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593132</v>
+        <v>593391</v>
       </c>
       <c r="R36" t="n">
-        <v>6980622</v>
+        <v>6980611</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>

--- a/artfynd/A 12199-2024 artfynd.xlsx
+++ b/artfynd/A 12199-2024 artfynd.xlsx
@@ -4061,7 +4061,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117980602</v>
+        <v>117980605</v>
       </c>
       <c r="B35" t="n">
         <v>57290</v>
@@ -4094,11 +4094,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
@@ -4113,10 +4109,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>593465</v>
+        <v>593120</v>
       </c>
       <c r="R35" t="n">
-        <v>6980521</v>
+        <v>6980627</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4143,12 +4139,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4175,7 +4171,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117980606</v>
+        <v>117980602</v>
       </c>
       <c r="B36" t="n">
         <v>57290</v>
@@ -4208,7 +4204,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593081</v>
+        <v>593465</v>
       </c>
       <c r="R36" t="n">
-        <v>6980689</v>
+        <v>6980521</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4285,7 +4285,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117980605</v>
+        <v>117980606</v>
       </c>
       <c r="B37" t="n">
         <v>57290</v>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>593120</v>
+        <v>593081</v>
       </c>
       <c r="R37" t="n">
-        <v>6980627</v>
+        <v>6980689</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>

--- a/artfynd/A 12199-2024 artfynd.xlsx
+++ b/artfynd/A 12199-2024 artfynd.xlsx
@@ -4061,7 +4061,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117980605</v>
+        <v>117980602</v>
       </c>
       <c r="B35" t="n">
         <v>57290</v>
@@ -4094,7 +4094,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
@@ -4109,10 +4113,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>593120</v>
+        <v>593465</v>
       </c>
       <c r="R35" t="n">
-        <v>6980627</v>
+        <v>6980521</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4139,12 +4143,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4171,7 +4175,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117980602</v>
+        <v>117980605</v>
       </c>
       <c r="B36" t="n">
         <v>57290</v>
@@ -4204,11 +4208,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593465</v>
+        <v>593120</v>
       </c>
       <c r="R36" t="n">
-        <v>6980521</v>
+        <v>6980627</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD36" t="b">
